--- a/outputs/step3_disease_logistic/fpca_cumulative_variance.xlsx
+++ b/outputs/step3_disease_logistic/fpca_cumulative_variance.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>n_components</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>elbow_chord_distance</t>
+  </si>
+  <si>
+    <t>is_elbow_reference</t>
   </si>
   <si>
     <t>selected_best_n</t>
@@ -386,10 +389,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -405,16 +408,19 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.8430388217978624</v>
+        <v>0.8422475216955621</v>
       </c>
       <c r="C2">
-        <v>0.8430388217978624</v>
+        <v>0.8422475216955621</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -422,327 +428,387 @@
       <c r="E2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.9476745386450782</v>
+        <v>0.9472142780859177</v>
       </c>
       <c r="C3">
-        <v>0.1046357168472158</v>
+        <v>0.1049667563903557</v>
       </c>
       <c r="D3">
-        <v>0.5821439698890992</v>
+        <v>0.5817837106278574</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.9736401715619721</v>
+        <v>0.9734806643597272</v>
       </c>
       <c r="C4">
-        <v>0.02596563291689391</v>
+        <v>0.02626638627380951</v>
       </c>
       <c r="D4">
-        <v>0.6109149679353165</v>
+        <v>0.610642145523012</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.9845647585950739</v>
+        <v>0.9844379588811943</v>
       </c>
       <c r="C5">
-        <v>0.01092458703310173</v>
+        <v>0.0109572945214671</v>
       </c>
       <c r="D5">
-        <v>0.5863149980938627</v>
+        <v>0.5862790750034251</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.9909111595941874</v>
+        <v>0.9908390297106054</v>
       </c>
       <c r="C6">
-        <v>0.006346400999113544</v>
+        <v>0.006401070829411104</v>
       </c>
       <c r="D6">
-        <v>0.5529389572288497</v>
+        <v>0.5528882038074334</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.9941593617045065</v>
+        <v>0.9941289276860358</v>
       </c>
       <c r="C7">
-        <v>0.003248202110319065</v>
+        <v>0.003289897975430334</v>
       </c>
       <c r="D7">
-        <v>0.5183215280162313</v>
+        <v>0.5182841092313837</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.9959977810116619</v>
+        <v>0.9959587363900356</v>
       </c>
       <c r="C8">
-        <v>0.001838419307155448</v>
+        <v>0.001829808703999847</v>
       </c>
       <c r="D8">
-        <v>0.48228788376322</v>
+        <v>0.4822938120720068</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.9972821989642564</v>
+        <v>0.9972610487465099</v>
       </c>
       <c r="C9">
-        <v>0.001284417952594485</v>
+        <v>0.001302312356474267</v>
       </c>
       <c r="D9">
-        <v>0.445536424411718</v>
+        <v>0.4455205365498305</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.9980026812031209</v>
+        <v>0.9979861327154135</v>
       </c>
       <c r="C10">
-        <v>0.0007204822388644505</v>
+        <v>0.0007250839689035837</v>
       </c>
       <c r="D10">
-        <v>0.4087932978337495</v>
+        <v>0.4087890146269955</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.9985276046957018</v>
+        <v>0.9985173331367515</v>
       </c>
       <c r="C11">
-        <v>0.000524923492580931</v>
+        <v>0.0005312004213380295</v>
       </c>
       <c r="D11">
-        <v>0.3717411828457132</v>
+        <v>0.3717356473335587</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.9988424755279468</v>
+        <v>0.9988357227334295</v>
       </c>
       <c r="C12">
-        <v>0.0003148708322450178</v>
+        <v>0.0003183895966779593</v>
       </c>
       <c r="D12">
-        <v>0.3347012251092275</v>
+        <v>0.334698170840976</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.9990757679633814</v>
+        <v>0.9990681581439733</v>
       </c>
       <c r="C13">
-        <v>0.0002332924354345733</v>
+        <v>0.000232435410543852</v>
       </c>
       <c r="D13">
-        <v>0.297553505319385</v>
+        <v>0.2975541891406041</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.9992518384978998</v>
+        <v>0.9992451382152537</v>
       </c>
       <c r="C14">
-        <v>0.0001760705345184022</v>
+        <v>0.0001769800712804193</v>
       </c>
       <c r="D14">
-        <v>0.2603853557100742</v>
+        <v>0.2603846014801418</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.9993773579913262</v>
+        <v>0.9993724232342753</v>
       </c>
       <c r="C15">
-        <v>0.0001255194934264292</v>
+        <v>0.0001272850190215946</v>
       </c>
       <c r="D15">
-        <v>0.2232116106956404</v>
+        <v>0.2232101776473555</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.9994655458015826</v>
+        <v>0.9994612079475511</v>
       </c>
       <c r="C16">
-        <v>8.818781025643485E-05</v>
+        <v>8.878471327578019E-05</v>
       </c>
       <c r="D16">
-        <v>0.1860267775059204</v>
+        <v>0.1860263550253741</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.9995312177155002</v>
+        <v>0.9995276292479036</v>
       </c>
       <c r="C17">
-        <v>6.567191391759764E-05</v>
+        <v>6.642130035250382E-05</v>
       </c>
       <c r="D17">
-        <v>0.1488295170831718</v>
+        <v>0.1488289843294162</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.9995806515870513</v>
+        <v>0.9995776414102272</v>
       </c>
       <c r="C18">
-        <v>4.943387155109669E-05</v>
+        <v>5.001216232358718E-05</v>
       </c>
       <c r="D18">
-        <v>0.1116269909020046</v>
+        <v>0.111626614594447</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.9996164148563256</v>
+        <v>0.9996135524046835</v>
       </c>
       <c r="C19">
-        <v>3.576326927423601E-05</v>
+        <v>3.591099445632295E-05</v>
       </c>
       <c r="D19">
-        <v>0.07442231119523351</v>
+        <v>0.07442230715369823</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.9996497721647654</v>
+        <v>0.9996470822613026</v>
       </c>
       <c r="C20">
-        <v>3.335730843978535E-05</v>
+        <v>3.352985661908559E-05</v>
       </c>
       <c r="D20">
-        <v>0.03720818289651222</v>
+        <v>0.03720815991072752</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.9996736353849048</v>
+        <v>0.9996710995650308</v>
       </c>
       <c r="C21">
-        <v>2.386322013947506E-05</v>
+        <v>2.401730372814104E-05</v>
       </c>
       <c r="D21">
         <v>3.14018491736755E-16</v>
       </c>
       <c r="E21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" t="b">
         <v>0</v>
       </c>
     </row>
